--- a/output/pdf_financials_xlsx/HMM.A.xlsx
+++ b/output/pdf_financials_xlsx/HMM.A.xlsx
@@ -2401,43 +2401,43 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.869</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.869</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.633</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.774</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.326</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.263</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.051</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.719</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>4.069</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0</v>
@@ -2521,43 +2521,43 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.869</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.869</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.633</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.416</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.774</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.326</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.263</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.051</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.719</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>4.069</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0</v>
@@ -3241,43 +3241,43 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.867</v>
+        <v>0.998</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.643</v>
+        <v>0.774</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.573</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.298</v>
+        <v>0.882</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.66</v>
+        <v>0.886</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.417</v>
+        <v>1.091</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.627</v>
+        <v>1.364</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.205</v>
+        <v>1.591</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.232</v>
+        <v>1.181</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.39</v>
+        <v>1.765</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.519</v>
+        <v>1.8</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>5.868</v>
+        <v>1.799</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.801</v>
+        <v>1.859</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0</v>
@@ -13802,7 +13802,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -21288,7 +21288,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -45235,7 +45235,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -47469,7 +47469,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -49753,7 +49753,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -51478,7 +51478,7 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -52805,7 +52805,7 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">

--- a/output/pdf_financials_xlsx/HMM.A.xlsx
+++ b/output/pdf_financials_xlsx/HMM.A.xlsx
@@ -1113,25 +1113,25 @@
         <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0</v>
+        <v>0.334</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0</v>
+        <v>0.349</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>-0</v>
+        <v>0.197</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>-0</v>
+        <v>0.616</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-0</v>
+        <v>0.926</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>1.58</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>1.076</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>-0</v>
@@ -1143,10 +1143,10 @@
         <v>-0</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>-0</v>
+        <v>1.495</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>-0</v>
+        <v>3.208</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>-0</v>
@@ -2037,25 +2037,25 @@
         <v>0.355</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>3.501</v>
+        <v>3.167</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2.455</v>
+        <v>2.106</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.603</v>
+        <v>2.406</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>3.07</v>
+        <v>2.454</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>4.974</v>
+        <v>4.048</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>5.058</v>
+        <v>3.478</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.224</v>
+        <v>0.148</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>6.387</v>
@@ -2067,10 +2067,10 @@
         <v>6.282</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>10.161</v>
+        <v>8.666</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>16.035</v>
+        <v>12.827</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>20.263</v>
@@ -2100,31 +2100,31 @@
         <v>0.052</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.048</v>
+        <v>2.13</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.064</v>
+        <v>2.008</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.063</v>
+        <v>2.304</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.075</v>
+        <v>2.149</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.075</v>
+        <v>2.176</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.078</v>
+        <v>3.364</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.056</v>
+        <v>3.011</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.053</v>
+        <v>2.794</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.048</v>
+        <v>3.533</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>1.144</v>
@@ -2157,34 +2157,34 @@
         <v>0.355</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3.553</v>
+        <v>3.219</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.503</v>
+        <v>4.236</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2.667</v>
+        <v>4.414</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3.133</v>
+        <v>4.758</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>5.049</v>
+        <v>6.197</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>5.133</v>
+        <v>5.654</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.302</v>
+        <v>3.512</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>6.443</v>
+        <v>9.398</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>5.105</v>
+        <v>7.846</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>6.33</v>
+        <v>9.815</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>9.077</v>
@@ -2217,34 +2217,34 @@
         <v>0.5114831570757572</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>4.521103999389212</v>
+        <v>4.096097318894983</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>2.927930562541673</v>
+        <v>4.95513937791711</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2.885582905058155</v>
+        <v>4.775764133080877</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>3.371137126624774</v>
+        <v>5.1196522337953</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>4.796147123641614</v>
+        <v>5.886655520936241</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>4.381038544262743</v>
+        <v>4.825714383257655</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1.125090733123639</v>
+        <v>3.034806954477896</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>5.057061676844104</v>
+        <v>7.37641869299719</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>3.506133157511573</v>
+        <v>5.388662243650499</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>4.259987078712178</v>
+        <v>6.605335415096371</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>4.774152150130438</v>
@@ -6389,40 +6389,40 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>2.008</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>2.304</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>2.149</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>2.176</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>3.364</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>3.011</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>2.794</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>3.533</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>6.79</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>7.562</v>
       </c>
       <c r="P100" s="1" t="inlineStr">
         <is>
@@ -7202,19 +7202,19 @@
         <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.109</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="P112" s="1" t="inlineStr">
         <is>
@@ -29016,7 +29016,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -29099,7 +29103,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -29180,7 +29184,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -31302,7 +31310,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -45512,7 +45524,11 @@
           <t>Net finance expense</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -48306,7 +48322,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E407" t="inlineStr">
         <is>
           <t>-</t>
@@ -51682,7 +51702,11 @@
           <t>Net finance costs</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>InterestExpenseNonOperating</t>
+        </is>
+      </c>
       <c r="E441" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HMM.A.xlsx
+++ b/output/pdf_financials_xlsx/HMM.A.xlsx
@@ -6782,10 +6782,10 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>-1.01</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.878</v>
+        <v>-1.331</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>-2.286</v>
@@ -7181,7 +7181,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -7442,10 +7442,10 @@
         </is>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.064</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>0</v>
@@ -7910,7 +7910,7 @@
         <v>0</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>0</v>
+        <v>1.303</v>
       </c>
       <c r="F123" s="3" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>-1.515</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>-1.846</v>
+        <v>-0.543</v>
       </c>
       <c r="F125" s="3" t="n">
         <v>-1.368</v>
@@ -8343,40 +8343,26 @@
       <c r="H129" s="3" t="n">
         <v>-4.301</v>
       </c>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I129" s="3" t="n">
+        <v>9.462</v>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>7.566</v>
+      </c>
+      <c r="K129" s="3" t="n">
+        <v>-2.229</v>
+      </c>
+      <c r="L129" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M129" s="3" t="n">
+        <v>-8.789</v>
+      </c>
+      <c r="N129" s="3" t="n">
+        <v>-1.298</v>
+      </c>
+      <c r="O129" s="3" t="n">
+        <v>11.091</v>
       </c>
       <c r="P129" s="1" t="inlineStr">
         <is>
@@ -8753,40 +8739,26 @@
       <c r="H135" s="3" t="n">
         <v>3.596</v>
       </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I135" s="3" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="K135" s="3" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="L135" s="3" t="n">
+        <v>-6.09</v>
+      </c>
+      <c r="M135" s="3" t="n">
+        <v>9.657999999999999</v>
+      </c>
+      <c r="N135" s="3" t="n">
+        <v>2.817</v>
+      </c>
+      <c r="O135" s="3" t="n">
+        <v>-15.345</v>
       </c>
       <c r="P135" s="1" t="inlineStr">
         <is>
@@ -14421,7 +14393,11 @@
           <t>Intangible assets and goodwill 7</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -19666,7 +19642,11 @@
           <t>Intangible assets and goodwill 10</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -30323,7 +30303,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -30677,7 +30661,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -32351,7 +32339,11 @@
           <t>Net cash generated (used) from operating activities</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -33077,7 +33069,11 @@
           <t>Cash generated from (used) in operating activities</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -33176,7 +33172,11 @@
           <t>Net cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -33471,7 +33471,11 @@
           <t>Cash generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -34164,7 +34168,11 @@
           <t>Cash generated on operating activities</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -34263,7 +34271,11 @@
           <t>Net cash generated on operating activities</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E262" t="inlineStr">
         <is>
           <t>-</t>
@@ -36172,7 +36184,11 @@
           <t>Net cash generated (used) in operating activities</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -36370,7 +36386,11 @@
           <t>Increase of long-term debt</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -36974,7 +36994,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -37370,7 +37394,11 @@
           <t>Change in non-cash operating working capital</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -38081,7 +38109,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -38180,7 +38212,11 @@
           <t>Proceeds from the disposition of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
